--- a/2026/GENERAL PAZ 138/Junio/Junio GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Junio/Junio GRAL PAZ 138.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3DFD8E-F6D2-4D4E-9641-D24BBAAC7B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18641FC-AA92-4735-B01A-E48332EECE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -308,13 +308,19 @@
     <t>FED. PATRONAL - Seguro integral - Póliza Nº 2318491</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>Transf 22/05</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Abril y Mayo</t>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>Debito 18/06</t>
+  </si>
+  <si>
+    <t>Transf 12/06</t>
+  </si>
+  <si>
+    <t>Escribania Rabolini - Digitalizacion reglamento original</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - SE ADEUDA JUNIO</t>
   </si>
 </sst>
 </file>
@@ -330,7 +336,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,16 +412,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -431,14 +427,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -615,6 +603,13 @@
       <b/>
       <sz val="10"/>
       <name val="Arial1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1284,65 +1279,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="29" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="30" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="29" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="32" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="33" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="29" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="30" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="29" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="32" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="33" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="34" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="34" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1352,61 +1341,59 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="16" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="14" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1415,7 +1402,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="16" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1429,41 +1416,38 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1486,8 +1470,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1499,7 +1483,7 @@
     <xf numFmtId="10" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1517,7 +1501,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="41" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="39" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1525,7 +1509,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1535,22 +1519,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1562,17 +1555,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1580,16 +1576,10 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1601,16 +1591,14 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2054,676 +2042,705 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="151" t="s">
+      <c r="A4" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="151"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:4" hidden="1">
-      <c r="A5" s="151"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:4" hidden="1">
-      <c r="A6" s="151"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="A6" s="142"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="151"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
+      <c r="A7" s="142"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="149" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="159"/>
+      <c r="B10" s="149"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="159"/>
+      <c r="B11" s="149"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="170" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
+      <c r="B14" s="170"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="170"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
+      <c r="A15" s="170"/>
+      <c r="B15" s="170"/>
+      <c r="C15" s="170"/>
+      <c r="D15" s="170"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
+      <c r="A16" s="170"/>
+      <c r="B16" s="170"/>
+      <c r="C16" s="170"/>
+      <c r="D16" s="170"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
+      <c r="A17" s="170"/>
+      <c r="B17" s="170"/>
+      <c r="C17" s="170"/>
+      <c r="D17" s="170"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A18" s="60"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+    </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
+      <c r="A19" s="171"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
+      <c r="A20" s="60"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+    </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="8"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="G22" s="22"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="54"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="120">
-        <v>0</v>
-      </c>
-      <c r="D23" s="54"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="111">
+        <v>0</v>
+      </c>
+      <c r="D23" s="46"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="121" t="s">
+      <c r="A24" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="76">
+      <c r="B24" s="112"/>
+      <c r="C24" s="68">
         <f>SUM(C23:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="55"/>
+      <c r="D24" s="47"/>
     </row>
     <row r="25" spans="1:7" ht="0.6" customHeight="1">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="80"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="72"/>
     </row>
     <row r="26" spans="1:7" hidden="1">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="80"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="72"/>
     </row>
     <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="54"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="80"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="72"/>
     </row>
     <row r="28" spans="1:7" hidden="1">
-      <c r="A28" s="54"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="80"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="72"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="121" t="s">
+      <c r="A29" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="122"/>
-      <c r="C29" s="27">
+      <c r="B29" s="113"/>
+      <c r="C29" s="21">
         <f>SUM(C25:C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="55"/>
+      <c r="D29" s="47"/>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A30" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="56">
+      <c r="A30" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="48">
         <f>C24+C29</f>
         <v>0</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="57"/>
-      <c r="F31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="49"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A32" s="105" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="123"/>
-      <c r="C32" s="91">
-        <f>65000*2</f>
-        <v>130000</v>
-      </c>
-      <c r="D32" s="89"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="9"/>
+      <c r="A32" s="96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="114"/>
+      <c r="C32" s="82">
+        <v>0</v>
+      </c>
+      <c r="D32" s="81"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="56">
+      <c r="B33" s="9"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="48">
         <f>SUM(C32:C32)</f>
-        <v>130000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="33"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="26"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A35" s="152" t="s">
+      <c r="A35" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="153"/>
-      <c r="C35" s="179">
+      <c r="B35" s="144"/>
+      <c r="C35" s="141">
         <v>87914</v>
       </c>
-      <c r="D35" s="88"/>
+      <c r="D35" s="80" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="58">
+      <c r="B36" s="9"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="50">
         <f>SUM(C35:C35)</f>
         <v>87914</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="124"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="59"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="51"/>
     </row>
     <row r="38" spans="1:6" hidden="1">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="93"/>
-      <c r="D38" s="88"/>
-      <c r="F38" s="82"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="80"/>
+      <c r="F38" s="74"/>
     </row>
     <row r="39" spans="1:6" hidden="1">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="88"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="80"/>
     </row>
     <row r="40" spans="1:6" hidden="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="88"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="80"/>
     </row>
     <row r="41" spans="1:6" hidden="1">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="94"/>
-      <c r="D41" s="87"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="79"/>
     </row>
     <row r="42" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="124"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="58">
+      <c r="B42" s="115"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="50">
         <f>SUM(C38:C41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="124"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="59"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="51"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A44" s="68" t="s">
+      <c r="A44" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="54"/>
-      <c r="C44" s="94">
-        <v>36475.68</v>
-      </c>
-      <c r="D44" s="86" t="s">
-        <v>93</v>
+      <c r="B44" s="46"/>
+      <c r="C44" s="85">
+        <v>36019.040000000001</v>
+      </c>
+      <c r="D44" s="78" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A45" s="54" t="s">
+      <c r="A45" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="94">
-        <v>197470.88</v>
-      </c>
-      <c r="D45" s="86" t="s">
-        <v>93</v>
+      <c r="B45" s="46"/>
+      <c r="C45" s="85">
+        <v>204474.88</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="58">
+      <c r="B46" s="9"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="50">
         <f>SUM(C44:C45)</f>
-        <v>233946.56</v>
+        <v>240493.92</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="61"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="53"/>
     </row>
     <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A48" s="152"/>
-      <c r="B48" s="153"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="84"/>
+      <c r="A48" s="143" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="144"/>
+      <c r="C48" s="85">
+        <v>150000</v>
+      </c>
+      <c r="D48" s="76"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="63">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="55">
         <f>SUM(C48:C48)</f>
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="125"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="61"/>
+      <c r="B50" s="116"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="53"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="54"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="96"/>
-      <c r="D51" s="64"/>
+      <c r="A51" s="46"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="87"/>
+      <c r="D51" s="56"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="126" t="s">
+      <c r="A52" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B52" s="126"/>
-      <c r="C52" s="65"/>
-      <c r="D52" s="58">
+      <c r="B52" s="117"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="50">
         <f>SUM(C51:C51)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="66"/>
+      <c r="A53" s="46"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="58"/>
     </row>
     <row r="54" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A54" s="156" t="s">
+      <c r="A54" s="146" t="s">
         <v>75</v>
       </c>
-      <c r="B54" s="157"/>
-      <c r="C54" s="158"/>
-      <c r="D54" s="67">
-        <f>1000000-451860.56</f>
-        <v>548139.43999999994</v>
+      <c r="B54" s="147"/>
+      <c r="C54" s="148"/>
+      <c r="D54" s="59">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="127"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="69"/>
-      <c r="E55" s="23"/>
+      <c r="A55" s="118"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="60"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="128" t="s">
+      <c r="A56" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B56" s="129"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="71">
+      <c r="B56" s="120"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="63">
         <f>(SUM(D25:D54))</f>
-        <v>1000000</v>
-      </c>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+        <v>478407.92000000004</v>
+      </c>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="68"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="F57" s="83"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="F57" s="75"/>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="68"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
+      <c r="A58" s="60"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="130" t="s">
+      <c r="A59" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B59" s="131"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="73"/>
+      <c r="B59" s="122"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="65"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="152"/>
-      <c r="B60" s="153"/>
-      <c r="C60" s="94"/>
-      <c r="D60" s="84"/>
+      <c r="A60" s="143"/>
+      <c r="B60" s="144"/>
+      <c r="C60" s="85"/>
+      <c r="D60" s="76"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="152"/>
-      <c r="B61" s="153"/>
-      <c r="C61" s="94"/>
-      <c r="D61" s="60"/>
+      <c r="A61" s="143"/>
+      <c r="B61" s="144"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="52"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="134"/>
-      <c r="B62" s="135"/>
-      <c r="C62" s="94"/>
-      <c r="D62" s="60"/>
+      <c r="A62" s="125"/>
+      <c r="B62" s="126"/>
+      <c r="C62" s="85"/>
+      <c r="D62" s="52"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="136"/>
-      <c r="B63" s="137"/>
-      <c r="C63" s="138"/>
-      <c r="D63" s="28">
+      <c r="A63" s="127"/>
+      <c r="B63" s="128"/>
+      <c r="C63" s="129"/>
+      <c r="D63" s="129">
         <f>SUM(C60:C62)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1">
-      <c r="A64" s="68"/>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
+      <c r="A64" s="60"/>
+      <c r="B64" s="60"/>
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
     </row>
     <row r="65" spans="1:4" hidden="1">
-      <c r="A65" s="68"/>
-      <c r="B65" s="68"/>
-      <c r="C65" s="68"/>
+      <c r="A65" s="60"/>
+      <c r="B65" s="60"/>
+      <c r="C65" s="60"/>
+      <c r="D65" s="60"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="139" t="s">
+      <c r="A66" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="139"/>
-      <c r="C66" s="140"/>
-      <c r="D66" s="90">
+      <c r="B66" s="130"/>
+      <c r="C66" s="131"/>
+      <c r="D66" s="172">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A67" s="68"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
+      <c r="A67" s="60"/>
+      <c r="B67" s="60"/>
+      <c r="C67" s="60"/>
+      <c r="D67" s="60"/>
     </row>
     <row r="68" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A68" s="128" t="s">
+      <c r="A68" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B68" s="129"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="34">
+      <c r="B68" s="120"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="63">
         <f>D63+D66</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A69" s="68"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
+      <c r="A69" s="60"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
     </row>
     <row r="70" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A70" s="141" t="s">
+      <c r="A70" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="B70" s="142">
+      <c r="B70" s="133">
         <f>D56</f>
-        <v>1000000</v>
-      </c>
-      <c r="C70" s="143"/>
+        <v>478407.92000000004</v>
+      </c>
+      <c r="C70" s="134"/>
+      <c r="D70" s="60"/>
     </row>
     <row r="71" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A71" s="141" t="s">
+      <c r="A71" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="142">
+      <c r="B71" s="133">
         <f>D56-D54</f>
-        <v>451860.56000000006</v>
-      </c>
-      <c r="C71" s="68"/>
+        <v>478407.92000000004</v>
+      </c>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="141" t="s">
+      <c r="A72" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="B72" s="142">
+      <c r="B72" s="133">
         <f>D68-D66</f>
         <v>0</v>
       </c>
-      <c r="C72" s="68"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
     </row>
     <row r="73" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A73" s="141" t="s">
+      <c r="A73" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="B73" s="142">
+      <c r="B73" s="133">
         <f>D68</f>
         <v>0</v>
       </c>
-      <c r="C73" s="68"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="68"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="68"/>
+      <c r="A74" s="60"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="68"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="68"/>
+      <c r="A75" s="60"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="68"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
+      <c r="A76" s="60"/>
+      <c r="B76" s="60"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
     </row>
     <row r="77" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A77" s="144" t="s">
+      <c r="A77" s="135" t="s">
         <v>44</v>
       </c>
-      <c r="B77" s="145"/>
-      <c r="C77" s="68"/>
+      <c r="B77" s="136"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
     </row>
     <row r="78" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="146">
-        <v>7678.890000000014</v>
-      </c>
-      <c r="C78" s="68"/>
+      <c r="B78" s="137">
+        <v>87629.729999999981</v>
+      </c>
+      <c r="C78" s="60"/>
     </row>
     <row r="79" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A79" s="147" t="s">
+      <c r="A79" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="54">
         <f>PRORRATEO!H18</f>
-        <v>531811.4</v>
-      </c>
-      <c r="C79" s="68"/>
+        <v>951360.18000000017</v>
+      </c>
+      <c r="C79" s="60"/>
     </row>
     <row r="80" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A80" s="147" t="s">
+      <c r="A80" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B80" s="62">
+      <c r="B80" s="54">
         <f>B89</f>
         <v>0</v>
       </c>
-      <c r="C80" s="68"/>
+      <c r="C80" s="60"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="149" t="s">
+      <c r="A81" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="62">
+      <c r="B81" s="54">
         <f>-B71</f>
-        <v>-451860.56000000006</v>
-      </c>
-      <c r="C81" s="68"/>
+        <v>-478407.92000000004</v>
+      </c>
+      <c r="C81" s="60"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="148" t="s">
+      <c r="A82" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="B82" s="62">
+      <c r="B82" s="54">
         <f>-(B72)</f>
         <v>0</v>
       </c>
-      <c r="C82" s="68"/>
+      <c r="C82" s="60"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="106">
+      <c r="B83" s="97">
         <f>SUM(B78:B82)</f>
-        <v>87629.729999999981</v>
-      </c>
-      <c r="C83" s="133"/>
+        <v>560581.99000000011</v>
+      </c>
+      <c r="C83" s="124"/>
     </row>
     <row r="84" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B84" s="22"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="133"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="124"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="155" t="s">
+      <c r="A85" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="B85" s="155"/>
+      <c r="B85" s="145"/>
     </row>
     <row r="86" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A86" s="155"/>
-      <c r="B86" s="155"/>
+      <c r="A86" s="145"/>
+      <c r="B86" s="145"/>
     </row>
     <row r="87" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A87" s="74"/>
-      <c r="B87" s="18"/>
+      <c r="A87" s="66"/>
+      <c r="B87" s="12"/>
     </row>
     <row r="88" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A88" s="74"/>
-      <c r="B88" s="18"/>
+      <c r="A88" s="66"/>
+      <c r="B88" s="12"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="24" t="s">
+      <c r="A89" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B89" s="75">
+      <c r="B89" s="67">
         <f>SUM(B87:B88)</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:12">
-      <c r="L90" s="4"/>
+      <c r="L90" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2750,7 +2767,7 @@
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="5.140625" customWidth="1"/>
@@ -2771,1021 +2788,1014 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
-      <c r="A1" s="107"/>
-      <c r="B1" s="160" t="str">
+      <c r="A1" s="98"/>
+      <c r="B1" s="154" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="109"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="100"/>
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A2" s="110"/>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="118">
+      <c r="N2" s="2"/>
+      <c r="O2" s="109">
         <v>1000000</v>
       </c>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="9"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="4"/>
       <c r="R2">
         <v>1406361.51</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A3" s="113"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114" t="s">
+      <c r="A3" s="104"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="115"/>
-      <c r="O3" s="119">
-        <v>0</v>
-      </c>
-      <c r="P3" s="116"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="110">
+        <v>0</v>
+      </c>
+      <c r="P3" s="107"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="173" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="166" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="174"/>
-      <c r="E4" s="174"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="175"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="167"/>
+      <c r="L4" s="167"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="168"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="178" t="s">
+      <c r="B5" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="165" t="s">
+      <c r="D5" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="165" t="s">
+      <c r="F5" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="165" t="s">
+      <c r="G5" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="165" t="s">
+      <c r="I5" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="169" t="s">
+      <c r="J5" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="167" t="s">
+      <c r="K5" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="167" t="s">
+      <c r="L5" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="167" t="s">
+      <c r="M5" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="171" t="s">
+      <c r="N5" s="164" t="s">
         <v>48</v>
       </c>
-      <c r="O5" s="95" t="s">
+      <c r="O5" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="163" t="s">
+      <c r="P5" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="23"/>
-      <c r="T5" s="22"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="177"/>
-      <c r="B6" s="178"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="166"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="172"/>
-      <c r="O6" s="29" t="str">
+      <c r="A6" s="151"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="159"/>
+      <c r="J6" s="163"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="160"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="165"/>
+      <c r="O6" s="22" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="P6" s="163"/>
-      <c r="S6" s="22">
+        <v>VTO 17/07</v>
+      </c>
+      <c r="P6" s="157"/>
+      <c r="S6" s="16">
         <v>65160</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="16">
         <v>157470</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="17">
         <f>T6+S6</f>
         <v>222630</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="77">
         <v>1</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="35">
+      <c r="E7" s="77"/>
+      <c r="F7" s="90">
         <v>11.2</v>
       </c>
-      <c r="G7" s="36">
-        <v>1187511.01</v>
-      </c>
-      <c r="H7" s="37">
-        <v>0</v>
-      </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39">
+      <c r="G7" s="29">
+        <v>1335136.01</v>
+      </c>
+      <c r="H7" s="29">
+        <v>0</v>
+      </c>
+      <c r="I7" s="30"/>
+      <c r="J7" s="91">
         <f>G7-H7</f>
-        <v>1187511.01</v>
-      </c>
-      <c r="K7" s="39">
+        <v>1335136.01</v>
+      </c>
+      <c r="K7" s="91">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>35625.330300000001</v>
-      </c>
-      <c r="L7" s="150">
+        <v>40054.080300000001</v>
+      </c>
+      <c r="L7" s="169">
         <f>O$3*F7%</f>
         <v>0</v>
       </c>
-      <c r="M7" s="40">
+      <c r="M7" s="92">
         <f>O$2*F7%</f>
         <v>111999.99999999999</v>
       </c>
-      <c r="N7" s="41">
-        <v>0</v>
-      </c>
-      <c r="O7" s="42">
+      <c r="N7" s="93">
+        <v>0</v>
+      </c>
+      <c r="O7" s="94">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1335136.01</v>
-      </c>
-      <c r="P7" s="43">
+        <v>1487190.01</v>
+      </c>
+      <c r="P7" s="95">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1375190.01</v>
-      </c>
-      <c r="Q7" s="23">
+        <v>1531806.01</v>
+      </c>
+      <c r="Q7" s="17">
         <v>0.01</v>
       </c>
-      <c r="S7" s="22">
+      <c r="S7" s="16">
         <v>66960</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="16">
         <v>161820</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="17">
         <f t="shared" ref="U7:U16" si="1">T7+S7</f>
         <v>228780</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="24">
         <v>2</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="35">
+      <c r="E8" s="25"/>
+      <c r="F8" s="27">
         <v>11.2</v>
       </c>
-      <c r="G8" s="36">
-        <v>815685.02</v>
-      </c>
-      <c r="H8" s="37">
-        <v>300000</v>
-      </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39">
+      <c r="G8" s="28">
+        <v>643156.02</v>
+      </c>
+      <c r="H8" s="29">
+        <v>350000</v>
+      </c>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31">
         <f t="shared" ref="J8:J16" si="2">G8-H8</f>
-        <v>515685.02</v>
-      </c>
-      <c r="K8" s="39">
+        <v>293156.02</v>
+      </c>
+      <c r="K8" s="31">
         <f t="shared" ref="K8:K16" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>15470.5506</v>
-      </c>
-      <c r="L8" s="40">
+        <v>8794.6805999999997</v>
+      </c>
+      <c r="L8" s="32">
         <f t="shared" ref="L8:L17" si="4">O$3*F8%</f>
         <v>0</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M8" s="32">
         <f t="shared" ref="M8:M17" si="5">O$2*F8%</f>
         <v>111999.99999999999</v>
       </c>
-      <c r="N8" s="41">
-        <v>0</v>
-      </c>
-      <c r="O8" s="42">
+      <c r="N8" s="33">
+        <v>0</v>
+      </c>
+      <c r="O8" s="34">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>643156.02</v>
-      </c>
-      <c r="P8" s="43">
+        <v>413951.02</v>
+      </c>
+      <c r="P8" s="35">
         <f t="shared" si="0"/>
-        <v>662451.02</v>
-      </c>
-      <c r="Q8" s="23">
+        <v>426370.02</v>
+      </c>
+      <c r="Q8" s="17">
         <f>Q7+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="R8" s="23"/>
-      <c r="S8" s="22">
+      <c r="R8" s="17"/>
+      <c r="S8" s="16">
         <v>41700</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="16">
         <v>100775</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="17">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="85" t="s">
+      <c r="C9" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="97" t="s">
+      <c r="D9" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="99">
+      <c r="E9" s="77"/>
+      <c r="F9" s="90">
         <v>8.9</v>
       </c>
-      <c r="G9" s="37">
-        <v>23806.03</v>
-      </c>
-      <c r="H9" s="37">
-        <f>G9</f>
-        <v>23806.03</v>
-      </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="100">
+      <c r="G9" s="29">
+        <v>89000.03</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0</v>
+      </c>
+      <c r="I9" s="30"/>
+      <c r="J9" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="39">
+        <v>89000.03</v>
+      </c>
+      <c r="K9" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="101">
+        <v>2670.0009</v>
+      </c>
+      <c r="L9" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="92">
         <f t="shared" si="5"/>
         <v>89000.000000000015</v>
       </c>
-      <c r="N9" s="102">
-        <v>0</v>
-      </c>
-      <c r="O9" s="103">
+      <c r="N9" s="93">
+        <v>0</v>
+      </c>
+      <c r="O9" s="94">
         <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>89000.03</v>
-      </c>
-      <c r="P9" s="104">
+        <v>180670.03</v>
+      </c>
+      <c r="P9" s="95">
         <f t="shared" si="0"/>
-        <v>91670.03</v>
-      </c>
-      <c r="Q9" s="23">
+        <v>186090.03</v>
+      </c>
+      <c r="Q9" s="17">
         <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
         <v>0.03</v>
       </c>
-      <c r="S9" s="22">
+      <c r="S9" s="16">
         <v>44220</v>
       </c>
-      <c r="T9" s="22">
+      <c r="T9" s="16">
         <v>106865</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="17">
         <f t="shared" si="1"/>
         <v>151085</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="24">
         <v>4</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="99">
+      <c r="E10" s="24"/>
+      <c r="F10" s="90">
         <v>8.9</v>
       </c>
-      <c r="G10" s="36">
-        <v>28024.04</v>
-      </c>
-      <c r="H10" s="37">
-        <v>28050</v>
-      </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39">
+      <c r="G10" s="28">
+        <v>91643.04</v>
+      </c>
+      <c r="H10" s="29">
+        <v>89000</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31">
         <f t="shared" si="2"/>
-        <v>-25.959999999999127</v>
-      </c>
-      <c r="K10" s="39">
+        <v>2643.0399999999936</v>
+      </c>
+      <c r="K10" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="40">
+        <v>79.291199999999805</v>
+      </c>
+      <c r="L10" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="40">
+      <c r="M10" s="32">
         <f t="shared" si="5"/>
         <v>89000.000000000015</v>
       </c>
-      <c r="N10" s="41">
-        <v>0</v>
-      </c>
-      <c r="O10" s="42">
+      <c r="N10" s="33">
+        <v>0</v>
+      </c>
+      <c r="O10" s="34">
         <f t="shared" si="6"/>
-        <v>88974.04</v>
-      </c>
-      <c r="P10" s="43">
+        <v>91722.04</v>
+      </c>
+      <c r="P10" s="35">
         <f t="shared" si="0"/>
-        <v>91643.04</v>
-      </c>
-      <c r="Q10" s="23">
+        <v>94474.04</v>
+      </c>
+      <c r="Q10" s="17">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="S10" s="22">
+      <c r="S10" s="16">
         <v>64080</v>
       </c>
-      <c r="T10" s="22">
+      <c r="T10" s="16">
         <v>154860</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="17">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="24">
         <v>5</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="35">
+      <c r="E11" s="25"/>
+      <c r="F11" s="27">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G11" s="36">
-        <v>26235.05</v>
-      </c>
-      <c r="H11" s="37">
+      <c r="G11" s="28">
+        <v>98000.05</v>
+      </c>
+      <c r="H11" s="29">
         <f>G11</f>
-        <v>26235.05</v>
-      </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39">
+        <v>98000.05</v>
+      </c>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="32">
         <f t="shared" si="5"/>
         <v>98000</v>
       </c>
-      <c r="N11" s="41">
-        <v>0</v>
-      </c>
-      <c r="O11" s="42">
+      <c r="N11" s="33">
+        <v>0</v>
+      </c>
+      <c r="O11" s="34">
         <f t="shared" si="6"/>
         <v>98000.05</v>
       </c>
-      <c r="P11" s="43">
+      <c r="P11" s="35">
         <f t="shared" si="0"/>
         <v>100940.05</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="17">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="S11" s="22">
+      <c r="S11" s="16">
         <v>41700</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="16">
         <v>100775</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="17">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="24">
         <v>6</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="35">
+      <c r="E12" s="24"/>
+      <c r="F12" s="27">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G12" s="36">
-        <v>30858.06</v>
-      </c>
-      <c r="H12" s="37">
+      <c r="G12" s="28">
+        <v>98000.06</v>
+      </c>
+      <c r="H12" s="29">
         <f>G12</f>
-        <v>30858.06</v>
-      </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39">
+        <v>98000.06</v>
+      </c>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K12" s="39">
+      <c r="K12" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="40">
+      <c r="M12" s="32">
         <f t="shared" si="5"/>
         <v>98000</v>
       </c>
-      <c r="N12" s="132">
-        <v>0</v>
-      </c>
-      <c r="O12" s="42">
+      <c r="N12" s="123">
+        <v>0</v>
+      </c>
+      <c r="O12" s="34">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
         <v>98000.06</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="35">
         <f t="shared" si="0"/>
         <v>100940.06</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="17">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="S12" s="22">
+      <c r="S12" s="16">
         <v>41340</v>
       </c>
-      <c r="T12" s="22">
+      <c r="T12" s="16">
         <v>99905</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="17">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="24">
         <v>7</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="99">
+      <c r="E13" s="24"/>
+      <c r="F13" s="90">
         <v>8.9</v>
       </c>
-      <c r="G13" s="36">
-        <v>28024.07</v>
-      </c>
-      <c r="H13" s="37">
+      <c r="G13" s="28">
+        <v>89000.07</v>
+      </c>
+      <c r="H13" s="29">
         <f>G13</f>
-        <v>28024.07</v>
-      </c>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39">
+        <v>89000.07</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="32">
         <f t="shared" si="5"/>
         <v>89000.000000000015</v>
       </c>
-      <c r="N13" s="41">
-        <v>0</v>
-      </c>
-      <c r="O13" s="42">
+      <c r="N13" s="33">
+        <v>0</v>
+      </c>
+      <c r="O13" s="34">
         <f t="shared" si="6"/>
         <v>89000.07</v>
       </c>
-      <c r="P13" s="43">
+      <c r="P13" s="35">
         <f t="shared" si="0"/>
         <v>91670.07</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="Q13" s="17">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R13" s="83"/>
-      <c r="S13" s="117">
+      <c r="R13" s="75"/>
+      <c r="S13" s="108">
         <v>64080</v>
       </c>
-      <c r="T13" s="22">
+      <c r="T13" s="16">
         <v>154860</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="17">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="24">
         <v>8</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="99">
+      <c r="F14" s="90">
         <v>8.9</v>
       </c>
-      <c r="G14" s="36">
-        <v>28024.080000000002</v>
-      </c>
-      <c r="H14" s="37">
-        <v>28865</v>
-      </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39">
+      <c r="G14" s="28">
+        <v>88159.08</v>
+      </c>
+      <c r="H14" s="29">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30"/>
+      <c r="J14" s="31">
         <f t="shared" si="2"/>
-        <v>-840.91999999999825</v>
-      </c>
-      <c r="K14" s="39">
+        <v>88159.08</v>
+      </c>
+      <c r="K14" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="40">
+        <v>2644.7723999999998</v>
+      </c>
+      <c r="L14" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="40">
+      <c r="M14" s="32">
         <f t="shared" si="5"/>
         <v>89000.000000000015</v>
       </c>
-      <c r="N14" s="41">
-        <v>0</v>
-      </c>
-      <c r="O14" s="42">
+      <c r="N14" s="33">
+        <v>0</v>
+      </c>
+      <c r="O14" s="34">
         <f t="shared" si="6"/>
-        <v>88159.08</v>
-      </c>
-      <c r="P14" s="43">
+        <v>179804.08</v>
+      </c>
+      <c r="P14" s="35">
         <f t="shared" si="0"/>
-        <v>90804.08</v>
-      </c>
-      <c r="Q14" s="23">
+        <v>185198.07999999999</v>
+      </c>
+      <c r="Q14" s="17">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="S14" s="22">
+      <c r="S14" s="16">
         <v>41700</v>
       </c>
-      <c r="T14" s="22">
+      <c r="T14" s="16">
         <v>100775</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="17">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="85">
+      <c r="B15" s="77">
         <v>9</v>
       </c>
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="85" t="s">
+      <c r="D15" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="98" t="s">
+      <c r="E15" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="27">
         <v>11.2</v>
       </c>
-      <c r="G15" s="37">
-        <v>30707.09</v>
-      </c>
-      <c r="H15" s="37">
-        <v>30707.09</v>
-      </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="100">
+      <c r="G15" s="29">
+        <v>115360.09</v>
+      </c>
+      <c r="H15" s="29">
+        <v>115360</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="100">
-        <v>0</v>
-      </c>
-      <c r="L15" s="101">
+        <v>8.999999999650754E-2</v>
+      </c>
+      <c r="K15" s="91">
+        <v>0</v>
+      </c>
+      <c r="L15" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="101">
+      <c r="M15" s="92">
         <f t="shared" si="5"/>
         <v>111999.99999999999</v>
       </c>
-      <c r="N15" s="102">
-        <v>0</v>
-      </c>
-      <c r="O15" s="103">
+      <c r="N15" s="93">
+        <v>0</v>
+      </c>
+      <c r="O15" s="94">
         <f t="shared" si="6"/>
         <v>112000.09</v>
       </c>
-      <c r="P15" s="104">
+      <c r="P15" s="95">
         <f t="shared" si="0"/>
         <v>115360.09</v>
       </c>
-      <c r="Q15" s="23">
+      <c r="Q15" s="17">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
-      <c r="S15" s="22">
+      <c r="S15" s="16">
         <v>41340</v>
       </c>
-      <c r="T15" s="22">
+      <c r="T15" s="16">
         <v>99905</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="17">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="16.149999999999999" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="85">
+      <c r="B16" s="77">
         <v>10</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="35">
+      <c r="E16" s="89"/>
+      <c r="F16" s="27">
         <v>11.2</v>
       </c>
-      <c r="G16" s="36">
-        <v>35266.1</v>
-      </c>
-      <c r="H16" s="37">
-        <f>G16</f>
-        <v>35266.1</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39">
+      <c r="G16" s="28">
+        <v>112000.1</v>
+      </c>
+      <c r="H16" s="29">
+        <v>112000</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="39">
+        <v>0.10000000000582077</v>
+      </c>
+      <c r="K16" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="40">
+        <v>3.000000000174623E-3</v>
+      </c>
+      <c r="L16" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="40">
+      <c r="M16" s="32">
         <f t="shared" si="5"/>
         <v>111999.99999999999</v>
       </c>
-      <c r="N16" s="41">
-        <v>0</v>
-      </c>
-      <c r="O16" s="42">
+      <c r="N16" s="33">
+        <v>0</v>
+      </c>
+      <c r="O16" s="34">
         <f t="shared" si="6"/>
         <v>112000.1</v>
       </c>
-      <c r="P16" s="43">
+      <c r="P16" s="35">
         <f t="shared" si="0"/>
         <v>115360.1</v>
       </c>
-      <c r="Q16" s="23">
+      <c r="Q16" s="17">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="16">
         <v>71280</v>
       </c>
-      <c r="T16" s="22">
+      <c r="T16" s="16">
         <v>172260</v>
       </c>
-      <c r="U16" s="23">
+      <c r="U16" s="17">
         <f t="shared" si="1"/>
         <v>243540</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="44" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="37"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="46" t="e">
+      <c r="H17" s="29"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="38" t="e">
         <f t="shared" ref="J17" si="8">G17-H17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="40">
+      <c r="K17" s="31"/>
+      <c r="L17" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="39">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="48">
-        <v>0</v>
-      </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="23"/>
+      <c r="N17" s="40">
+        <v>0</v>
+      </c>
+      <c r="O17" s="34"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="52">
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44">
         <f>SUM(F7:F17)</f>
         <v>100.00000000000001</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="20">
         <f>SUM(G7:G17)</f>
-        <v>2234140.5499999998</v>
-      </c>
-      <c r="H18" s="30">
+        <v>2759454.55</v>
+      </c>
+      <c r="H18" s="23">
         <f>SUM(H7:H17)</f>
-        <v>531811.4</v>
-      </c>
-      <c r="I18" s="30">
+        <v>951360.18000000017</v>
+      </c>
+      <c r="I18" s="23">
         <f>SUM(I7:I17)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30">
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23">
         <f>SUM(L7:L17)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="23">
         <f>SUM(M7:M17)</f>
         <v>1000000</v>
       </c>
-      <c r="N18" s="30">
+      <c r="N18" s="23">
         <f>SUM(N7:N17)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="53">
+      <c r="O18" s="45">
         <f>SUM(O7:O16)</f>
-        <v>2753425.55</v>
-      </c>
-      <c r="P18" s="53">
+        <v>2862337.55</v>
+      </c>
+      <c r="P18" s="45">
         <f>SUM(P7:P16)</f>
-        <v>2836028.55</v>
+        <v>2948208.55</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="164" t="s">
+      <c r="D21" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
-      <c r="H21" s="164"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="164"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="164"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="164"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="158"/>
+      <c r="H21" s="158"/>
+      <c r="I21" s="158"/>
+      <c r="J21" s="158"/>
+      <c r="K21" s="158"/>
+      <c r="L21" s="158"/>
+      <c r="M21" s="158"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="158"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="164"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="164"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="164"/>
-      <c r="N22" s="164"/>
-      <c r="O22" s="164"/>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
+      <c r="F22" s="158"/>
+      <c r="G22" s="158"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="158"/>
+      <c r="J22" s="158"/>
+      <c r="K22" s="158"/>
+      <c r="L22" s="158"/>
+      <c r="M22" s="158"/>
+      <c r="N22" s="158"/>
+      <c r="O22" s="158"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="164"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="164"/>
-      <c r="N23" s="164"/>
-      <c r="O23" s="164"/>
+      <c r="D23" s="158"/>
+      <c r="E23" s="158"/>
+      <c r="F23" s="158"/>
+      <c r="G23" s="158"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="158"/>
+      <c r="L23" s="158"/>
+      <c r="M23" s="158"/>
+      <c r="N23" s="158"/>
+      <c r="O23" s="158"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="164"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="164"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="164"/>
-      <c r="N24" s="164"/>
-      <c r="O24" s="164"/>
+      <c r="D24" s="158"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="158"/>
+      <c r="G24" s="158"/>
+      <c r="H24" s="158"/>
+      <c r="I24" s="158"/>
+      <c r="J24" s="158"/>
+      <c r="K24" s="158"/>
+      <c r="L24" s="158"/>
+      <c r="M24" s="158"/>
+      <c r="N24" s="158"/>
+      <c r="O24" s="158"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="164"/>
-      <c r="E25" s="164"/>
-      <c r="F25" s="164"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="164"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="164"/>
-      <c r="N25" s="164"/>
-      <c r="O25" s="164"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
+      <c r="J25" s="158"/>
+      <c r="K25" s="158"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="158"/>
+      <c r="N25" s="158"/>
+      <c r="O25" s="158"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
-      <c r="G26" s="164"/>
-      <c r="H26" s="164"/>
-      <c r="I26" s="164"/>
-      <c r="J26" s="164"/>
-      <c r="K26" s="164"/>
-      <c r="L26" s="164"/>
-      <c r="M26" s="164"/>
-      <c r="N26" s="164"/>
-      <c r="O26" s="164"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="158"/>
+      <c r="G26" s="158"/>
+      <c r="H26" s="158"/>
+      <c r="I26" s="158"/>
+      <c r="J26" s="158"/>
+      <c r="K26" s="158"/>
+      <c r="L26" s="158"/>
+      <c r="M26" s="158"/>
+      <c r="N26" s="158"/>
+      <c r="O26" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3799,6 +3809,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>

--- a/2026/GENERAL PAZ 138/Junio/Junio GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Junio/Junio GRAL PAZ 138.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18641FC-AA92-4735-B01A-E48332EECE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35AC0F6-550F-4AF2-A649-EB1165EDFE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$90</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="103">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -257,9 +257,6 @@
     <t>Mes de DICIEMBRE</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>LUERCHO ROMINA</t>
   </si>
   <si>
@@ -320,7 +317,28 @@
     <t>Escribania Rabolini - Digitalizacion reglamento original</t>
   </si>
   <si>
-    <t>Honorarios administracion - SE ADEUDA JUNIO</t>
+    <t>Debito 24/07</t>
+  </si>
+  <si>
+    <t>Transf 31/07</t>
+  </si>
+  <si>
+    <t>Transf 24/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - Junio y Julio </t>
+  </si>
+  <si>
+    <t>Gustavo Padron - Sr. Contador - Gestion ARCA</t>
+  </si>
+  <si>
+    <t>Honorarios administrativos - Gestion ARCA</t>
+  </si>
+  <si>
+    <t>Escribania Romanatti - Digitalizacion rubrica de libro - Acta designacion - Documento administracion</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - COMPENSACION A UF 1 QUE NO ABONA EXPENSAS</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1339,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1510,94 +1528,98 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="8" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2028,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2051,7 +2073,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
@@ -2064,68 +2086,68 @@
       <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="142" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="142"/>
+      <c r="A4" s="145" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="145"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:4" hidden="1">
-      <c r="A5" s="142"/>
-      <c r="B5" s="142"/>
+      <c r="A5" s="145"/>
+      <c r="B5" s="145"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:4" hidden="1">
-      <c r="A6" s="142"/>
-      <c r="B6" s="142"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="145"/>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="142"/>
-      <c r="B7" s="142"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="145"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="149" t="s">
-        <v>92</v>
+      <c r="B9" s="153" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="149"/>
+      <c r="B10" s="153"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="149"/>
+      <c r="B11" s="153"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="170" t="s">
+      <c r="A14" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="170"/>
-      <c r="C14" s="170"/>
-      <c r="D14" s="170"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="170"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="170"/>
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="170"/>
-      <c r="B16" s="170"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="170"/>
+      <c r="A16" s="148"/>
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="170"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="170"/>
+      <c r="A17" s="148"/>
+      <c r="B17" s="148"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="60"/>
@@ -2134,7 +2156,7 @@
       <c r="D18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="171"/>
+      <c r="A19" s="143"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
@@ -2240,519 +2262,582 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B32" s="114"/>
       <c r="C32" s="82">
-        <v>0</v>
+        <f>65000*2</f>
+        <v>130000</v>
       </c>
       <c r="D32" s="81"/>
       <c r="F32" s="16"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A33" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="114"/>
+      <c r="C33" s="83">
+        <v>70000</v>
+      </c>
+      <c r="D33" s="81"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A34" s="96" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="114"/>
+      <c r="C34" s="83">
+        <v>130000</v>
+      </c>
+      <c r="D34" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A35" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="48">
-        <f>SUM(C32:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A34" s="8" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="48">
+        <f>SUM(C32:C34)</f>
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A36" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="26"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A35" s="143" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="141">
+      <c r="B36" s="9"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="26"/>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A37" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="147"/>
+      <c r="C37" s="141">
         <v>87914</v>
       </c>
-      <c r="D35" s="80" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="9" t="s">
+      <c r="D37" s="80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A38" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="147"/>
+      <c r="C38" s="141">
+        <v>87914</v>
+      </c>
+      <c r="D38" s="173" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="50">
-        <f>SUM(C35:C35)</f>
-        <v>87914</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1">
-      <c r="A37" s="8" t="s">
+      <c r="B39" s="9"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="50">
+        <f>SUM(C37:C38)</f>
+        <v>175828</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
+      <c r="A40" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="115"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="51"/>
-    </row>
-    <row r="38" spans="1:6" hidden="1">
-      <c r="A38" s="46" t="s">
+      <c r="B40" s="115"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="51"/>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
+      <c r="A41" s="46" t="s">
         <v>56</v>
-      </c>
-      <c r="B38" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="84"/>
-      <c r="D38" s="80"/>
-      <c r="F38" s="74"/>
-    </row>
-    <row r="39" spans="1:6" hidden="1">
-      <c r="A39" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="80"/>
-    </row>
-    <row r="40" spans="1:6" hidden="1">
-      <c r="A40" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="85"/>
-      <c r="D40" s="80"/>
-    </row>
-    <row r="41" spans="1:6" hidden="1">
-      <c r="A41" s="46" t="s">
-        <v>59</v>
       </c>
       <c r="B41" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="85"/>
-      <c r="D41" s="79"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A42" s="9" t="s">
+      <c r="C41" s="84"/>
+      <c r="D41" s="80"/>
+      <c r="F41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
+      <c r="A42" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="85"/>
+      <c r="D42" s="80"/>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
+      <c r="A43" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="85"/>
+      <c r="D43" s="80"/>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
+      <c r="A44" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="85"/>
+      <c r="D44" s="79"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
+      <c r="A45" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="115"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="50">
-        <f>SUM(C38:C41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="8" t="s">
+      <c r="B45" s="115"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="50">
+        <f>SUM(C41:C44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="115"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="51"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A44" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="85">
+      <c r="B46" s="115"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="51"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A47" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="46"/>
+      <c r="C47" s="85">
         <v>36019.040000000001</v>
       </c>
-      <c r="D44" s="78" t="s">
+      <c r="D47" s="78" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A48" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="46"/>
+      <c r="C48" s="85">
+        <v>207143.7</v>
+      </c>
+      <c r="D48" s="78" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A49" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="85">
+        <v>204474.88</v>
+      </c>
+      <c r="D49" s="78" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A50" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="50">
+        <f>SUM(C47:C49)</f>
+        <v>447637.62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="53"/>
+    </row>
+    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A52" s="146" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A45" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="46"/>
-      <c r="C45" s="85">
-        <v>204474.88</v>
-      </c>
-      <c r="D45" s="78" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="50">
-        <f>SUM(C44:C45)</f>
-        <v>240493.92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="53"/>
-    </row>
-    <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A48" s="143" t="s">
-        <v>95</v>
-      </c>
-      <c r="B48" s="144"/>
-      <c r="C48" s="85">
+      <c r="B52" s="147"/>
+      <c r="C52" s="85">
         <v>150000</v>
       </c>
-      <c r="D48" s="76"/>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="9" t="s">
+      <c r="D52" s="76"/>
+    </row>
+    <row r="53" spans="1:6" ht="33" customHeight="1">
+      <c r="A53" s="146" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="147"/>
+      <c r="C53" s="85">
+        <v>102680</v>
+      </c>
+      <c r="D53" s="174"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A54" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="55">
-        <f>SUM(C48:C48)</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="8" t="s">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="55">
+        <f>SUM(C52:C53)</f>
+        <v>252680</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A55" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="116"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="53"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="46"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="87"/>
-      <c r="D51" s="56"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="117" t="s">
+      <c r="B55" s="116"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="53"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="46"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="87"/>
+      <c r="D56" s="56"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B52" s="117"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="50">
-        <f>SUM(C51:C51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="46"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="58"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A54" s="146" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="147"/>
-      <c r="C54" s="148"/>
-      <c r="D54" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="118"/>
-      <c r="B55" s="60"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="17"/>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="119" t="s">
+      <c r="B57" s="117"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="50">
+        <f>SUM(C56:C56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A58" s="46"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="58"/>
+    </row>
+    <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A59" s="150" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="151"/>
+      <c r="C59" s="152"/>
+      <c r="D59" s="59">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A60" s="118"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="61"/>
+      <c r="E60" s="17"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A61" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B56" s="120"/>
-      <c r="C56" s="62"/>
-      <c r="D56" s="63">
-        <f>(SUM(D25:D54))</f>
-        <v>478407.92000000004</v>
-      </c>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="60"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="60"/>
-      <c r="F57" s="75"/>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="60"/>
-      <c r="B58" s="60"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="121" t="s">
+      <c r="B61" s="120"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="63">
+        <f>(SUM(D25:D59))</f>
+        <v>1341145.6200000001</v>
+      </c>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="60"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="F62" s="75"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A63" s="60"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B59" s="122"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="65"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="143"/>
-      <c r="B60" s="144"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="76"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="143"/>
-      <c r="B61" s="144"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="52"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="125"/>
-      <c r="B62" s="126"/>
-      <c r="C62" s="85"/>
-      <c r="D62" s="52"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="127"/>
-      <c r="B63" s="128"/>
-      <c r="C63" s="129"/>
-      <c r="D63" s="129">
-        <f>SUM(C60:C62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1">
-      <c r="A64" s="60"/>
-      <c r="B64" s="60"/>
-      <c r="C64" s="60"/>
-      <c r="D64" s="60"/>
-    </row>
-    <row r="65" spans="1:4" hidden="1">
-      <c r="A65" s="60"/>
-      <c r="B65" s="60"/>
-      <c r="C65" s="60"/>
-      <c r="D65" s="60"/>
+      <c r="B64" s="122"/>
+      <c r="C64" s="64"/>
+      <c r="D64" s="65"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="146"/>
+      <c r="B65" s="147"/>
+      <c r="C65" s="85"/>
+      <c r="D65" s="76"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="130" t="s">
-        <v>32</v>
-      </c>
-      <c r="B66" s="130"/>
-      <c r="C66" s="131"/>
-      <c r="D66" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A67" s="60"/>
-      <c r="B67" s="60"/>
-      <c r="C67" s="60"/>
-      <c r="D67" s="60"/>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A68" s="119" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="120"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="63">
-        <f>D63+D66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A66" s="146"/>
+      <c r="B66" s="147"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="52"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="125"/>
+      <c r="B67" s="126"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="52"/>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="127"/>
+      <c r="B68" s="128"/>
+      <c r="C68" s="129"/>
+      <c r="D68" s="129">
+        <f>SUM(C65:C67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" customHeight="1">
       <c r="A69" s="60"/>
       <c r="B69" s="60"/>
       <c r="C69" s="60"/>
       <c r="D69" s="60"/>
     </row>
-    <row r="70" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A70" s="132" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" s="133">
-        <f>D56</f>
-        <v>478407.92000000004</v>
-      </c>
-      <c r="C70" s="134"/>
+    <row r="70" spans="1:4" hidden="1">
+      <c r="A70" s="60"/>
+      <c r="B70" s="60"/>
+      <c r="C70" s="60"/>
       <c r="D70" s="60"/>
     </row>
-    <row r="71" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A71" s="132" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" s="133">
-        <f>D56-D54</f>
-        <v>478407.92000000004</v>
-      </c>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
+    <row r="71" spans="1:4">
+      <c r="A71" s="130" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" s="130"/>
+      <c r="C71" s="131"/>
+      <c r="D71" s="144">
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="B72" s="133">
-        <f>D68-D66</f>
-        <v>0</v>
-      </c>
+      <c r="A72" s="60"/>
+      <c r="B72" s="60"/>
       <c r="C72" s="60"/>
       <c r="D72" s="60"/>
     </row>
     <row r="73" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A73" s="132" t="s">
-        <v>49</v>
-      </c>
-      <c r="B73" s="133">
-        <f>D68</f>
-        <v>0</v>
-      </c>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="A73" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" s="120"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="63">
+        <f>D68+D71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
       <c r="A74" s="60"/>
       <c r="B74" s="60"/>
       <c r="C74" s="60"/>
       <c r="D74" s="60"/>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="60"/>
-      <c r="B75" s="60"/>
-      <c r="C75" s="60"/>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="132" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="133">
+        <f>D61</f>
+        <v>1341145.6200000001</v>
+      </c>
+      <c r="C75" s="134"/>
       <c r="D75" s="60"/>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="60"/>
-      <c r="B76" s="60"/>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="132" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="133">
+        <f>D61-D59</f>
+        <v>1206145.6200000001</v>
+      </c>
       <c r="C76" s="60"/>
       <c r="D76" s="60"/>
     </row>
     <row r="77" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A77" s="135" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="136"/>
+      <c r="A77" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="B77" s="133">
+        <f>D73-D71</f>
+        <v>0</v>
+      </c>
       <c r="C77" s="60"/>
       <c r="D77" s="60"/>
     </row>
-    <row r="78" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A78" s="7" t="s">
+    <row r="78" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A78" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="B78" s="133">
+        <f>D73</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="60"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="60"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="60"/>
+      <c r="B81" s="60"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
+    </row>
+    <row r="82" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A82" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" s="136"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+    </row>
+    <row r="83" spans="1:12" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A83" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="137">
+      <c r="B83" s="137">
         <v>87629.729999999981</v>
       </c>
-      <c r="C78" s="60"/>
-    </row>
-    <row r="79" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A79" s="138" t="s">
+      <c r="C83" s="60"/>
+    </row>
+    <row r="84" spans="1:12" ht="14.25" customHeight="1">
+      <c r="A84" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="B79" s="54">
+      <c r="B84" s="54">
         <f>PRORRATEO!H18</f>
         <v>951360.18000000017</v>
       </c>
-      <c r="C79" s="60"/>
-    </row>
-    <row r="80" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A80" s="138" t="s">
+      <c r="C84" s="60"/>
+    </row>
+    <row r="85" spans="1:12" ht="14.25" customHeight="1">
+      <c r="A85" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B80" s="54">
-        <f>B89</f>
-        <v>0</v>
-      </c>
-      <c r="C80" s="60"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="140" t="s">
+      <c r="B85" s="54">
+        <f>B94</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="60"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="54">
-        <f>-B71</f>
-        <v>-478407.92000000004</v>
-      </c>
-      <c r="C81" s="60"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" s="139" t="s">
+      <c r="B86" s="54">
+        <f>-B76</f>
+        <v>-1206145.6200000001</v>
+      </c>
+      <c r="C86" s="60"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="B82" s="54">
-        <f>-(B72)</f>
-        <v>0</v>
-      </c>
-      <c r="C82" s="60"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" s="6" t="s">
+      <c r="B87" s="54">
+        <f>-(B77)</f>
+        <v>0</v>
+      </c>
+      <c r="C87" s="60"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="97">
-        <f>SUM(B78:B82)</f>
-        <v>560581.99000000011</v>
-      </c>
-      <c r="C83" s="124"/>
-    </row>
-    <row r="84" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B84" s="16"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="124"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="145" t="s">
+      <c r="B88" s="97">
+        <f>SUM(B83:B87)</f>
+        <v>-167155.70999999996</v>
+      </c>
+      <c r="C88" s="124"/>
+    </row>
+    <row r="89" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B89" s="16"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="124"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="B85" s="145"/>
-    </row>
-    <row r="86" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A86" s="145"/>
-      <c r="B86" s="145"/>
-    </row>
-    <row r="87" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A87" s="66"/>
-      <c r="B87" s="12"/>
-    </row>
-    <row r="88" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A88" s="66"/>
-      <c r="B88" s="12"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="18" t="s">
+      <c r="B90" s="149"/>
+    </row>
+    <row r="91" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A91" s="149"/>
+      <c r="B91" s="149"/>
+    </row>
+    <row r="92" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A92" s="66"/>
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A93" s="66"/>
+      <c r="B93" s="12"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B89" s="67">
-        <f>SUM(B87:B88)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12">
-      <c r="L90" s="3"/>
+      <c r="B94" s="67">
+        <f>SUM(B92:B93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="L95" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A85:B86"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A53:B53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2767,7 +2852,7 @@
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="5.140625" customWidth="1"/>
@@ -2826,12 +2911,13 @@
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="109">
-        <v>1000000</v>
+        <f>R2</f>
+        <v>1341145.6200000001</v>
       </c>
       <c r="P2" s="103"/>
       <c r="Q2" s="4"/>
       <c r="R2">
-        <v>1406361.51</v>
+        <v>1341145.6200000001</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
@@ -2858,65 +2944,65 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
-      <c r="L4" s="167"/>
-      <c r="M4" s="167"/>
-      <c r="N4" s="167"/>
-      <c r="O4" s="167"/>
-      <c r="P4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="168"/>
+      <c r="I4" s="168"/>
+      <c r="J4" s="168"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="168"/>
+      <c r="M4" s="168"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="168"/>
+      <c r="P4" s="169"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="172" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="153" t="s">
+      <c r="C5" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="153" t="s">
+      <c r="D5" s="159" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="153" t="s">
+      <c r="E5" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="153" t="s">
+      <c r="F5" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="153" t="s">
+      <c r="G5" s="159" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="153" t="s">
+      <c r="H5" s="159" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="153" t="s">
+      <c r="I5" s="159" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="162" t="s">
+      <c r="J5" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="160" t="s">
+      <c r="K5" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="160" t="s">
+      <c r="L5" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="160" t="s">
+      <c r="M5" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="164" t="s">
+      <c r="N5" s="165" t="s">
         <v>48</v>
       </c>
       <c r="O5" s="86" t="s">
@@ -2929,20 +3015,20 @@
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="151"/>
-      <c r="B6" s="152"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="159"/>
-      <c r="J6" s="163"/>
-      <c r="K6" s="161"/>
-      <c r="L6" s="160"/>
-      <c r="M6" s="161"/>
-      <c r="N6" s="165"/>
+      <c r="A6" s="171"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="164"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="166"/>
       <c r="O6" s="22" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/07</v>
@@ -2970,7 +3056,7 @@
         <v>61</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" s="77"/>
       <c r="F7" s="90">
@@ -2991,24 +3077,24 @@
         <f>IF(J7&gt;0,J7*3%,0)</f>
         <v>40054.080300000001</v>
       </c>
-      <c r="L7" s="169">
+      <c r="L7" s="142">
         <f>O$3*F7%</f>
         <v>0</v>
       </c>
       <c r="M7" s="92">
         <f>O$2*F7%</f>
-        <v>111999.99999999999</v>
+        <v>150208.30943999998</v>
       </c>
       <c r="N7" s="93">
         <v>0</v>
       </c>
       <c r="O7" s="94">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1487190.01</v>
+        <v>1525398.01</v>
       </c>
       <c r="P7" s="95">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1531806.01</v>
+        <v>1571160.01</v>
       </c>
       <c r="Q7" s="17">
         <v>0.01</v>
@@ -3035,7 +3121,7 @@
         <v>62</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="27">
@@ -3061,19 +3147,19 @@
         <v>0</v>
       </c>
       <c r="M8" s="32">
-        <f t="shared" ref="M8:M17" si="5">O$2*F8%</f>
-        <v>111999.99999999999</v>
+        <f>O$2*F8%</f>
+        <v>150208.30943999998</v>
       </c>
       <c r="N8" s="33">
         <v>0</v>
       </c>
       <c r="O8" s="34">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>413951.02</v>
+        <v>452159.02</v>
       </c>
       <c r="P8" s="35">
         <f t="shared" si="0"/>
-        <v>426370.02</v>
+        <v>465724.02</v>
       </c>
       <c r="Q8" s="17">
         <f>Q7+0.01</f>
@@ -3102,7 +3188,7 @@
         <v>63</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="77"/>
       <c r="F9" s="90">
@@ -3128,22 +3214,22 @@
         <v>0</v>
       </c>
       <c r="M9" s="92">
-        <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
+        <f>O$2*F9%</f>
+        <v>119361.96018000002</v>
       </c>
       <c r="N9" s="93">
         <v>0</v>
       </c>
       <c r="O9" s="94">
-        <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>180670.03</v>
+        <f t="shared" ref="O9:O16" si="5">ROUND(SUM(J9:N9),0) + Q9</f>
+        <v>211032.03</v>
       </c>
       <c r="P9" s="95">
         <f t="shared" si="0"/>
-        <v>186090.03</v>
+        <v>217363.03</v>
       </c>
       <c r="Q9" s="17">
-        <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
+        <f t="shared" ref="Q9:Q16" si="6">Q8+0.01</f>
         <v>0.03</v>
       </c>
       <c r="S9" s="16">
@@ -3168,7 +3254,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="90">
@@ -3194,22 +3280,22 @@
         <v>0</v>
       </c>
       <c r="M10" s="32">
+        <f>O$2*F10%</f>
+        <v>119361.96018000002</v>
+      </c>
+      <c r="N10" s="33">
+        <v>0</v>
+      </c>
+      <c r="O10" s="34">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N10" s="33">
-        <v>0</v>
-      </c>
-      <c r="O10" s="34">
-        <f t="shared" si="6"/>
-        <v>91722.04</v>
+        <v>122084.04</v>
       </c>
       <c r="P10" s="35">
         <f t="shared" si="0"/>
-        <v>94474.04</v>
+        <v>125747.04</v>
       </c>
       <c r="Q10" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="S10" s="16">
@@ -3234,7 +3320,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="27">
@@ -3261,22 +3347,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="32">
+        <f>O$2*F11%</f>
+        <v>131432.27076000001</v>
+      </c>
+      <c r="N11" s="33">
+        <v>0</v>
+      </c>
+      <c r="O11" s="34">
         <f t="shared" si="5"/>
-        <v>98000</v>
-      </c>
-      <c r="N11" s="33">
-        <v>0</v>
-      </c>
-      <c r="O11" s="34">
-        <f t="shared" si="6"/>
-        <v>98000.05</v>
+        <v>131432.04999999999</v>
       </c>
       <c r="P11" s="35">
         <f t="shared" si="0"/>
-        <v>100940.05</v>
+        <v>135375.04999999999</v>
       </c>
       <c r="Q11" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
       <c r="S11" s="16">
@@ -3301,7 +3387,7 @@
         <v>66</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="27">
@@ -3328,22 +3414,22 @@
         <v>0</v>
       </c>
       <c r="M12" s="32">
-        <f t="shared" si="5"/>
-        <v>98000</v>
+        <f>O$2*F12%</f>
+        <v>131432.27076000001</v>
       </c>
       <c r="N12" s="123">
         <v>0</v>
       </c>
       <c r="O12" s="34">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>98000.06</v>
+        <v>131432.06</v>
       </c>
       <c r="P12" s="35">
         <f t="shared" si="0"/>
-        <v>100940.06</v>
+        <v>135375.06</v>
       </c>
       <c r="Q12" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="S12" s="16">
@@ -3368,7 +3454,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="90">
@@ -3395,22 +3481,22 @@
         <v>0</v>
       </c>
       <c r="M13" s="32">
+        <f>O$2*F13%</f>
+        <v>119361.96018000002</v>
+      </c>
+      <c r="N13" s="33">
+        <v>0</v>
+      </c>
+      <c r="O13" s="34">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N13" s="33">
-        <v>0</v>
-      </c>
-      <c r="O13" s="34">
-        <f t="shared" si="6"/>
-        <v>89000.07</v>
+        <v>119362.07</v>
       </c>
       <c r="P13" s="35">
         <f t="shared" si="0"/>
-        <v>91670.07</v>
+        <v>122943.07</v>
       </c>
       <c r="Q13" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="R13" s="75"/>
@@ -3436,10 +3522,10 @@
         <v>68</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="90">
         <v>8.9</v>
@@ -3464,22 +3550,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="32">
+        <f>O$2*F14%</f>
+        <v>119361.96018000002</v>
+      </c>
+      <c r="N14" s="33">
+        <v>0</v>
+      </c>
+      <c r="O14" s="34">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N14" s="33">
-        <v>0</v>
-      </c>
-      <c r="O14" s="34">
-        <f t="shared" si="6"/>
-        <v>179804.08</v>
+        <v>210166.08</v>
       </c>
       <c r="P14" s="35">
         <f t="shared" si="0"/>
-        <v>185198.07999999999</v>
+        <v>216471.08</v>
       </c>
       <c r="Q14" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
       <c r="S14" s="16">
@@ -3504,10 +3590,10 @@
         <v>69</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15" s="27">
         <v>11.2</v>
@@ -3531,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="M15" s="92">
+        <f>O$2*F15%</f>
+        <v>150208.30943999998</v>
+      </c>
+      <c r="N15" s="93">
+        <v>0</v>
+      </c>
+      <c r="O15" s="94">
         <f t="shared" si="5"/>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N15" s="93">
-        <v>0</v>
-      </c>
-      <c r="O15" s="94">
-        <f t="shared" si="6"/>
-        <v>112000.09</v>
+        <v>150208.09</v>
       </c>
       <c r="P15" s="95">
         <f t="shared" si="0"/>
-        <v>115360.09</v>
+        <v>154714.09</v>
       </c>
       <c r="Q15" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="S15" s="16">
@@ -3571,7 +3657,7 @@
         <v>70</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="89"/>
       <c r="F16" s="27">
@@ -3597,22 +3683,22 @@
         <v>0</v>
       </c>
       <c r="M16" s="32">
+        <f>O$2*F16%</f>
+        <v>150208.30943999998</v>
+      </c>
+      <c r="N16" s="33">
+        <v>0</v>
+      </c>
+      <c r="O16" s="34">
         <f t="shared" si="5"/>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N16" s="33">
-        <v>0</v>
-      </c>
-      <c r="O16" s="34">
-        <f t="shared" si="6"/>
-        <v>112000.1</v>
+        <v>150208.1</v>
       </c>
       <c r="P16" s="35">
         <f t="shared" si="0"/>
-        <v>115360.1</v>
+        <v>154714.1</v>
       </c>
       <c r="Q16" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="S16" s="16">
@@ -3641,7 +3727,7 @@
       <c r="H17" s="29"/>
       <c r="I17" s="37"/>
       <c r="J17" s="38" t="e">
-        <f t="shared" ref="J17" si="8">G17-H17</f>
+        <f t="shared" ref="J17" si="7">G17-H17</f>
         <v>#VALUE!</v>
       </c>
       <c r="K17" s="31"/>
@@ -3650,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="39">
-        <f t="shared" si="5"/>
+        <f>O$2*F17%</f>
         <v>0</v>
       </c>
       <c r="N17" s="40">
@@ -3689,7 +3775,7 @@
       </c>
       <c r="M18" s="23">
         <f>SUM(M7:M17)</f>
-        <v>1000000</v>
+        <v>1341145.6200000001</v>
       </c>
       <c r="N18" s="23">
         <f>SUM(N7:N17)</f>
@@ -3697,11 +3783,11 @@
       </c>
       <c r="O18" s="45">
         <f>SUM(O7:O16)</f>
-        <v>2862337.55</v>
+        <v>3203481.55</v>
       </c>
       <c r="P18" s="45">
         <f>SUM(P7:P16)</f>
-        <v>2948208.55</v>
+        <v>3299586.55</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -3796,6 +3882,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3809,11 +3900,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
